--- a/reports/acdr2026_staff_deployment/ACDR2026_会場準備一覧_案1009.xlsx
+++ b/reports/acdr2026_staff_deployment/ACDR2026_会場準備一覧_案1009.xlsx
@@ -613,7 +613,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -876,22 +875,22 @@
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>国名プレート・前方卓の席札の作成</t>
+          <t>卓上ネームプレートの名札リスト送付</t>
         </is>
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>U字28、側面列、教室型の指定席、前方卓（Day1モデレーター／Day2 TS登壇者・Co-Chair／SC用／閉会用）の卓上ネームプレート。COSEMが作る参加者名札（パス）とは別。COSEM（LO）が作るかをSylviaに確認し、ADRCが作る場合は神戸で印刷して確認する。</t>
+          <t>U字28、側面列、教室型の指定席、前方卓（Day1モデレーター／Day2 TS登壇者・Co-Chair／SC用／閉会用）の卓上ネームプレートはCOSEM（Sylvia）が作成する。ADRCは席と表記の一覧（名札リスト）を送り、届いた版を確認する。</t>
         </is>
       </c>
       <c r="G9" s="7" t="inlineStr">
         <is>
-          <t>藤本</t>
+          <t>吉田</t>
         </is>
       </c>
       <c r="H9" s="7" t="inlineStr">
         <is>
-          <t>Gerry</t>
+          <t>田中</t>
         </is>
       </c>
       <c r="I9" s="7" t="inlineStr">
@@ -903,12 +902,12 @@
       <c r="K9" s="6" t="inlineStr"/>
       <c r="L9" s="7" t="inlineStr">
         <is>
-          <t>COSEMが作るか【Sylviaに確認】。ADRC作成なら印刷確認ができる神戸の藤本（10/8藤本さん指摘で吉田→藤本）</t>
+          <t>10/13までに名札リストをSylviaへ（9/30の調整どおり）</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>担当を吉田→藤本。COSEMに作成可否を確認</t>
+          <t>作成はSylvia（10/9荒木田）。ADRCは名札リスト</t>
         </is>
       </c>
     </row>
@@ -2217,7 +2216,7 @@
       </c>
       <c r="F36" s="7" t="inlineStr">
         <is>
-          <t>受付（藤中・田中）、AV卓（池田・藤本・荒木田）、RT（吉田・Gerry）、記録・カードの配布（塩見・Mizan）。</t>
+          <t>受付（藤中・田中）、AV卓（池田・藤本・荒木田）、RT（吉田・Gerry）、記録（塩見）、フロア（Mizan）。</t>
         </is>
       </c>
       <c r="G36" s="7" t="inlineStr">
@@ -2265,7 +2264,7 @@
       </c>
       <c r="F37" s="7" t="inlineStr">
         <is>
-          <t>神戸が開始。届いたQRを情報スライドに貼る（藤本）。卓上の案内カード（ポケトークのQRと使い方をA6程度に印刷し、U字・側面列・教室型の卓に置くもの）を事務局部屋で印刷して置く。</t>
+          <t>神戸が開始。届いたQRを進行スライド（PPT 08）に貼り、参加者のWhatsAppに共有する（藤本）。卓上カードは作らない。</t>
         </is>
       </c>
       <c r="G37" s="7" t="inlineStr">
@@ -2275,7 +2274,7 @@
       </c>
       <c r="H37" s="7" t="inlineStr">
         <is>
-          <t>中村（神戸・Zoomホスト）、塩見・Mizan（カード印刷・配置）</t>
+          <t>中村（神戸・Zoomホスト）</t>
         </is>
       </c>
       <c r="I37" s="7" t="inlineStr">
@@ -2285,14 +2284,10 @@
       </c>
       <c r="J37" s="6" t="inlineStr"/>
       <c r="K37" s="6" t="inlineStr"/>
-      <c r="L37" s="7" t="inlineStr">
-        <is>
-          <t>案: QRは共有開始時にしか出ないので、共有開始を12:20に早めればカードをOpening前に置ける（6時間で失効するがDay1は16:15終了で足りる）。神戸と相談</t>
-        </is>
-      </c>
+      <c r="L37" s="7" t="n"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>卓上カードの説明を追記。田中→塩見・Mizan</t>
+          <t>QRはスライドとWhatsAppで共有（10/9荒木田）。卓上カードをやめた</t>
         </is>
       </c>
     </row>
@@ -2744,7 +2739,7 @@
       </c>
       <c r="F47" s="7" t="inlineStr">
         <is>
-          <t>QRをスライドに貼る（28日のQRは失効）。卓上カードを印刷して置く。</t>
+          <t>QRを進行スライドに貼り（28日のQRは失効）、参加者のWhatsAppに共有する。</t>
         </is>
       </c>
       <c r="G47" s="7" t="inlineStr">
@@ -2754,7 +2749,7 @@
       </c>
       <c r="H47" s="7" t="inlineStr">
         <is>
-          <t>中村（神戸）、塩見・Mizan（カード）</t>
+          <t>中村（神戸）</t>
         </is>
       </c>
       <c r="I47" s="7" t="inlineStr">
@@ -2764,14 +2759,10 @@
       </c>
       <c r="J47" s="6" t="inlineStr"/>
       <c r="K47" s="6" t="inlineStr"/>
-      <c r="L47" s="7" t="inlineStr">
-        <is>
-          <t>案: 共有開始を08:30に早めればカードをRT Part 2（09:00）前に置ける</t>
-        </is>
-      </c>
+      <c r="L47" s="7" t="n"/>
       <c r="M47" t="inlineStr">
         <is>
-          <t>田中→塩見・Mizan</t>
+          <t>QRはスライドとWhatsAppで共有</t>
         </is>
       </c>
     </row>
@@ -2913,7 +2904,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="10" t="inlineStr">
         <is>

--- a/reports/acdr2026_staff_deployment/ACDR2026_会場準備一覧_案1009.xlsx
+++ b/reports/acdr2026_staff_deployment/ACDR2026_会場準備一覧_案1009.xlsx
@@ -902,7 +902,7 @@
       <c r="K9" s="6" t="inlineStr"/>
       <c r="L9" s="7" t="inlineStr">
         <is>
-          <t>10/13までに名札リストをSylviaへ（9/30の調整どおり）</t>
+          <t>COSEMが印刷（Sylvia 9/28メール「Yes I'll get the nameplates for you guys」、約50枚）。ADRCは10/13までに氏名と席の一覧を送る</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">

--- a/reports/acdr2026_staff_deployment/ACDR2026_会場準備一覧_案1009.xlsx
+++ b/reports/acdr2026_staff_deployment/ACDR2026_会場準備一覧_案1009.xlsx
@@ -1484,7 +1484,7 @@
       </c>
       <c r="F22" s="7" t="inlineStr">
         <is>
-          <t>Zoom用（藤本）、進行スライド用（池田）、発表用（Gerry）。HDMI 2系統をスイッチャーへ、電源、切替をAVオペと確認。Zoomの音声はマイナスワン（会場→ZoomにZoomの戻りを入れない）をAVオペと確認（業者機材かADRCのATEM Miniかは業者の回答次第）。</t>
+          <t>Zoom用（藤本）、進行スライド用（池田）、発表用（Gerry）。HDMI 2系統をスイッチャーへ、電源、切替をAVオペと確認。Zoom PCには業者スイッチャーのHDMI出力（スクリーンと同じ）とマイナスワンの音声出力を受け、Zoomの音声をミキサーに戻す。有線LANを接続。</t>
         </is>
       </c>
       <c r="G22" s="7" t="inlineStr">
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E23" s="7" t="inlineStr">
         <is>
-          <t>カメラの設置・画角確認</t>
+          <t>カメラの画角確認（業者カメラ）</t>
         </is>
       </c>
       <c r="F23" s="7" t="inlineStr">
         <is>
-          <t>U字の内側（中央）。演台・ステージ・U字の発言者・教室型を振れるか。映像をAV卓のZoom用PCへ。業者カメラの場合は業者オペと確認し、ADRCのカメラは予備。</t>
+          <t>業者のカメラ（会場スクリーン用、Zoomにも同じ映像）。U字の発言者・演台・前方卓が入るかを業者のカメラオペと確認。</t>
         </is>
       </c>
       <c r="G23" s="7" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H23" s="7" t="inlineStr">
         <is>
-          <t>塩見</t>
+          <t>業者カメラオペ</t>
         </is>
       </c>
       <c r="I23" s="7" t="inlineStr">
@@ -1559,7 +1559,7 @@
       <c r="K23" s="6" t="inlineStr"/>
       <c r="L23" s="7" t="inlineStr">
         <is>
-          <t>業者カメラかADRCカメラか【TBC】</t>
+          <t>ADRCのカメラ・ATEMは持参しない（10/9）</t>
         </is>
       </c>
     </row>
